--- a/图谱数据.xlsx
+++ b/图谱数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\new qingzanggaoyuan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75DC601-96B3-456F-B77B-1281694D1DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FB9953-EF36-4605-9A4D-DCACC8BD81FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A82E885B-262B-48D9-B0FA-B6DD3A0651DD}"/>
   </bookViews>
@@ -100,10 +100,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>退出（逐步有序退出）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>格尔木市生态保护红线青海格尔木昆仑山国家级地质自然公园</t>
   </si>
   <si>
@@ -904,6 +900,10 @@
   </si>
   <si>
     <t>Action</t>
+  </si>
+  <si>
+    <t>限制（逐步有序退出）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1404,13 +1404,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="C1" s="15" t="s">
         <v>103</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1476,15 +1476,15 @@
         <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2</v>
@@ -1492,32 +1492,32 @@
     </row>
     <row r="9" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>1</v>
@@ -1525,32 +1525,32 @@
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>2</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2</v>
@@ -1580,32 +1580,32 @@
     </row>
     <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>2</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>2</v>
@@ -1624,21 +1624,21 @@
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>2</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>2</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="24" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>2</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>2</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>2</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
@@ -1701,13 +1701,13 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1715,18 +1715,18 @@
         <v>0</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>54</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>55</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>2</v>
@@ -1734,43 +1734,43 @@
     </row>
     <row r="31" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="C31" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B32" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>64</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>2</v>
@@ -1778,32 +1778,32 @@
     </row>
     <row r="35" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="C35" s="11" t="s">
         <v>66</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B36" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>68</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>2</v>
@@ -1811,21 +1811,21 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
         <v>75</v>
-      </c>
-      <c r="B39" t="s">
-        <v>76</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>2</v>
@@ -1833,123 +1833,123 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B40" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>77</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" s="12" t="s">
         <v>79</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="12" t="s">
         <v>81</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="C45" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="C46" s="14" t="s">
         <v>90</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="C47" s="14" t="s">
         <v>93</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" s="14" t="s">
         <v>95</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" t="s">
         <v>97</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>100</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>
